--- a/结果/策略二_单板反包_交易明细.xlsx
+++ b/结果/策略二_单板反包_交易明细.xlsx
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,9 +492,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>000581.XSHE</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>000581</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +502,7 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>23.30328</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,13 +510,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>23.81071378292822</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.070769806220134</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>386.0458288791481</v>
       </c>
     </row>
@@ -525,9 +526,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>000596.XSHE</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>000596</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -535,7 +536,7 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>93.14305</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,13 +544,13 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>91.56071502781118</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>-1.803636843922316</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>-335.9924734705969</v>
       </c>
     </row>
@@ -559,9 +560,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>000688.XSHE</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>000688</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -569,7 +570,7 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46.95690999999999</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,13 +578,13 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>42.39119190338959</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>-9.823489606920749</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>-1845.122869432451</v>
       </c>
     </row>
@@ -593,9 +594,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>000830.XSHE</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>000830</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -603,7 +604,7 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>16.40639</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -611,13 +612,13 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>16.52811128814539</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.6387423080586292</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>125.7534649861202</v>
       </c>
     </row>
@@ -627,9 +628,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>000859.XSHE</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>000859</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -637,7 +638,7 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>12.06205</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -645,13 +646,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>11.9619152989804</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>-0.9335552275282964</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>-180.169437315323</v>
       </c>
     </row>
@@ -661,9 +662,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>001267.XSHE</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>001267</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +672,7 @@
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>37.45742</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,13 +680,13 @@
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>44.60020315568775</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>18.95395485828536</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>3549.831238939174</v>
       </c>
     </row>
@@ -695,9 +696,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>001267.XSHE</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>001267</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -705,7 +706,7 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>47.96792</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -713,13 +714,13 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>44.06036292081198</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>-8.246151893760731</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>-1582.203017391053</v>
       </c>
     </row>
@@ -729,9 +730,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>001301.XSHE</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>001301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -739,7 +740,7 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>63.92385999999999</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -747,13 +748,13 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>63.37045704685993</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>-0.969425904767463</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>-185.9083374501859</v>
       </c>
     </row>
@@ -763,9 +764,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>002015.XSHE</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>002015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -773,7 +774,7 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>22.14212</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -781,13 +782,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>20.76371608410326</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>-6.324263184422911</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>-1260.293349069668</v>
       </c>
     </row>
@@ -797,9 +798,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>002034.XSHE</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>002034</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -807,7 +808,7 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>22.48246</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -815,13 +816,13 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>22.86275662173309</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.58306426990646</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>284.7294330048096</v>
       </c>
     </row>
@@ -831,9 +832,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>002077.XSHE</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>002077</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -841,7 +842,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>13.82381</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -849,13 +850,13 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>13.82403225215624</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>-0.1020637547479357</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>-19.75273934930886</v>
       </c>
     </row>
@@ -865,9 +866,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>002129.XSHE</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>002129</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -875,7 +876,7 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>11.68167</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -883,13 +884,13 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>11.97819508123698</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>2.434729213411889</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>483.5089545774333</v>
       </c>
     </row>
@@ -899,9 +900,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>002141.XSHE</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>002141</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +910,7 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>4.524519999999999</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -917,13 +918,13 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>5.664477268824056</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>25.08001761389562</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>4992.901816954612</v>
       </c>
     </row>
@@ -933,9 +934,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>002162.XSHE</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>002162</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -943,7 +944,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>4.4044</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -951,13 +952,13 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>3.9881249607828</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>-9.548979410803311</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>-1892.588621262394</v>
       </c>
     </row>
@@ -967,9 +968,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>002174.XSHE</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>002174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -977,7 +978,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>13.62361</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -985,13 +986,13 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>13.65123776748595</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.0982598810570819</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>18.74116017435301</v>
       </c>
     </row>
@@ -1001,9 +1002,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>002222.XSHE</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1012,7 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>80.55046999999999</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -1019,13 +1020,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>80.37299717273133</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>-0.3342855237551687</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>-53.85371210535</v>
       </c>
     </row>
@@ -1035,9 +1036,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>002245.XSHE</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>002245</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1045,7 +1046,7 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>22.70268</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -1053,13 +1054,13 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>21.01735788747404</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <v>-7.526723681294752</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>-1367.014393478854</v>
       </c>
     </row>
@@ -1069,9 +1070,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>002290.XSHE</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>002290</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1079,7 +1080,7 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>83.87379</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -1087,13 +1088,13 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>76.73992092134127</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>-8.612756352405952</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>-1444.769035245725</v>
       </c>
     </row>
@@ -1103,9 +1104,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>002309.XSHE</t>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>002309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1113,7 +1114,7 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>4.744739999999999</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -1121,13 +1122,13 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <v>4.931450919469983</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <v>3.830926030090195</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>763.4234148244261</v>
       </c>
     </row>
@@ -1137,9 +1138,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>002426.XSHE</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>002426</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,7 +1148,7 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>4.06406</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -1155,13 +1156,13 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>4.061389404310208</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <v>-0.1678951888633718</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>-33.43446994135167</v>
       </c>
     </row>
@@ -1171,9 +1172,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>002428.XSHE</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>002428</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1181,7 +1182,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>127.61749</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -1189,13 +1190,13 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>118.5048814733479</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="6" t="n">
         <v>-7.267281460482794</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>-927.4322191103482</v>
       </c>
     </row>
@@ -1205,9 +1206,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>002440.XSHE</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>002440</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1215,7 +1216,7 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>12.012</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -1223,13 +1224,13 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>12.44035618553924</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="4" t="n">
         <v>3.460218813558268</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>665.0263742153904</v>
       </c>
     </row>
@@ -1239,9 +1240,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>002484.XSHE</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>002484</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1249,7 +1250,7 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>30.39036</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -1257,13 +1258,13 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="3" t="n">
         <v>29.94483993994703</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="6" t="n">
         <v>-1.572085683384493</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>-286.6574992134045</v>
       </c>
     </row>
@@ -1273,9 +1274,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>002580.XSHE</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>002580</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1283,7 +1284,7 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>17.57756</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -1291,13 +1292,13 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>18.67538361713208</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="4" t="n">
         <v>6.138693236128487</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>1186.935735476069</v>
       </c>
     </row>
@@ -1307,9 +1308,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>002631.XSHE</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>002631</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1317,7 +1318,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>14.43442</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -1325,13 +1326,13 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>13.85880148826446</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>-4.091076415864733</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>-767.6800981029206</v>
       </c>
     </row>
@@ -1341,9 +1342,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>002636.XSHE</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>002636</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1351,7 +1352,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>78.58851</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -1359,13 +1360,13 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>83.83872670675179</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="4" t="n">
         <v>6.561611959599878</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>1031.334614206269</v>
       </c>
     </row>
@@ -1375,9 +1376,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>002785.XSHE</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>002785</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,7 +1386,7 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>46.78674</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -1393,13 +1394,13 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="3" t="n">
         <v>47.11108161768898</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="4" t="n">
         <v>0.5874465685447766</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>109.9388394655865</v>
       </c>
     </row>
@@ -1409,9 +1410,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>002859.XSHE</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>002859</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1419,7 +1420,7 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>88.94886</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -1427,13 +1428,13 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>95.00222706884919</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>6.693763635019123</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>1190.805288888814</v>
       </c>
     </row>
@@ -1443,9 +1444,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>300209.XSHE</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>300209</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1453,7 +1454,7 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>18.018</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -1461,13 +1462,13 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="3" t="n">
         <v>22.68392995390341</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>25.78027561625049</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>5109.599066589614</v>
       </c>
     </row>
@@ -1477,9 +1478,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>300345.XSHE</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>300345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1487,7 +1488,7 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>7.447439999999999</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -1495,13 +1496,13 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>8.084770920472717</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>8.449709686242841</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>1636.146353548522</v>
       </c>
     </row>
@@ -1511,9 +1512,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>300368.XSHE</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>300368</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1521,7 +1522,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>12.4124</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -1529,13 +1530,13 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>12.70612707017181</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>2.262840557555549</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>449.3965141856399</v>
       </c>
     </row>
@@ -1545,9 +1546,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>300534.XSHE</t>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>300534</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1555,7 +1556,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>10.02001</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -1563,13 +1564,13 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>10.62564541704642</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="4" t="n">
         <v>5.936650561117094</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="5" t="n">
         <v>1130.220661789079</v>
       </c>
     </row>
@@ -1579,9 +1580,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>300975.XSHE</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>300975</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1589,7 +1590,7 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>28.89887</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -1597,13 +1598,13 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="3" t="n">
         <v>35.35330983707627</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>22.21351213280207</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>3851.672396215617</v>
       </c>
     </row>
@@ -1613,9 +1614,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>301127.XSHE</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>301127</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1623,7 +1624,7 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>19.26925</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -1631,13 +1632,13 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>18.78948184154419</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="6" t="n">
         <v>-2.592438661053213</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>-499.5434866949961</v>
       </c>
     </row>
@@ -1647,9 +1648,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>600032.XSHG</t>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>600032</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1657,7 +1658,7 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>11.36135</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -1665,13 +1666,13 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="3" t="n">
         <v>11.04820161045311</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="6" t="n">
         <v>-2.858629817842031</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>-552.1241959759725</v>
       </c>
     </row>
@@ -1681,9 +1682,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>600095.XSHG</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>600095</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1691,7 +1692,7 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>8.908899999999999</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -1699,13 +1700,13 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>9.001031244646025</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="4" t="n">
         <v>0.9305994585841439</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="5" t="n">
         <v>182.3935853647661</v>
       </c>
     </row>
@@ -1715,9 +1716,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>600105.XSHG</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>600105</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1725,7 +1726,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>72.88280999999999</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -1733,13 +1734,13 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="3" t="n">
         <v>63.18711122735191</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="6" t="n">
         <v>-13.4169539120048</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="7" t="n">
         <v>-1955.730605494805</v>
       </c>
     </row>
@@ -1749,9 +1750,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>600126.XSHG</t>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>600126</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1759,7 +1760,7 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>6.416409999999999</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -1767,13 +1768,13 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>6.486973959253068</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="4" t="n">
         <v>0.9969068682057052</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="5" t="n">
         <v>198.2934591449368</v>
       </c>
     </row>
@@ -1783,9 +1784,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>600162.XSHG</t>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>600162</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1793,7 +1794,7 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="3" t="n">
         <v>3.593589999999999</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -1801,13 +1802,13 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="3" t="n">
         <v>3.263799223748967</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="6" t="n">
         <v>-9.275110170423632</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <v>-1833.201873653296</v>
       </c>
     </row>
@@ -1817,9 +1818,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>600183.XSHG</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>600183</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1827,7 +1828,7 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>99.05895999999998</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -1835,13 +1836,13 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>101.7750138145895</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>2.637982437877503</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>522.63159358882</v>
       </c>
     </row>
@@ -1851,9 +1852,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>600184.XSHG</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>600184</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1861,7 +1862,7 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>20.50048</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -1869,13 +1870,13 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="3" t="n">
         <v>21.3081066873601</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>3.831341690723521</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>706.8990933345935</v>
       </c>
     </row>
@@ -1885,9 +1886,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>600186.XSHG</t>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>600186</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1895,7 +1896,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>13.08307</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -1903,13 +1904,13 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>12.02166671908546</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="6" t="n">
         <v>-8.211618743215034</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <v>-1611.497742461915</v>
       </c>
     </row>
@@ -1919,9 +1920,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>600227.XSHG</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>600227</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1929,7 +1930,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>4.12412</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -1937,13 +1938,13 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="3" t="n">
         <v>4.939714433589522</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="4" t="n">
         <v>19.66360350074825</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>3892.562902536282</v>
       </c>
     </row>
@@ -1953,9 +1954,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>600237.XSHG</t>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>600237</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1963,7 +1964,7 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>11.32131</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -1971,13 +1972,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>11.37191500867774</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.3428027850322748</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>65.97660216963362</v>
       </c>
     </row>
@@ -1987,9 +1988,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>600362.XSHG</t>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>600362</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1997,7 +1998,7 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="3" t="n">
         <v>53.28322999999999</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -2005,13 +2006,13 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="3" t="n">
         <v>46.19784589039971</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="6" t="n">
         <v>-13.40536445826899</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="7" t="n">
         <v>-2142.843352991315</v>
       </c>
     </row>
@@ -2021,9 +2022,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>600392.XSHG</t>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>600392</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2031,7 +2032,7 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>33.77374</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -2039,13 +2040,13 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>30.28503702696541</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="6" t="n">
         <v>-10.435581251346</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>-1762.243039659173</v>
       </c>
     </row>
@@ -2055,9 +2056,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>600488.XSHG</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>600488</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2065,7 +2066,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>5.145139999999999</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -2073,13 +2074,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>5.777134270937449</v>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="4" t="n">
         <v>12.1739136760497</v>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="H48" s="5" t="n">
         <v>2380.186628025233</v>
       </c>
     </row>
@@ -2089,9 +2090,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>600497.XSHG</t>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>600497</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2099,7 +2100,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>12.2122</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -2107,13 +2108,13 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="3" t="n">
         <v>12.78267430797155</v>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="4" t="n">
         <v>4.565786853101719</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="5" t="n">
         <v>892.1328353191809</v>
       </c>
     </row>
@@ -2123,9 +2124,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>600563.XSHG</t>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>600563</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2133,7 +2134,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>188.188</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -2141,13 +2142,13 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="3" t="n">
         <v>191.0268228107945</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="4" t="n">
         <v>1.402595941909693</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="5" t="n">
         <v>263.9517251161012</v>
       </c>
     </row>
@@ -2157,9 +2158,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>600578.XSHG</t>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>600578</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2167,7 +2168,7 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>8.128119999999999</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -2175,13 +2176,13 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="3" t="n">
         <v>9.20626743677699</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="4" t="n">
         <v>13.15438616208383</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="5" t="n">
         <v>2566.090302042164</v>
       </c>
     </row>
@@ -2191,9 +2192,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>600596.XSHG</t>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>600596</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2201,7 +2202,7 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>12.26225</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -2209,13 +2210,13 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>12.15977277765292</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="G52" s="6" t="n">
         <v>-0.9382562658866386</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H52" s="7" t="n">
         <v>-184.0821263418949</v>
       </c>
     </row>
@@ -2225,9 +2226,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>600611.XSHG</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>600611</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2235,7 +2236,7 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>5.08508</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -2243,13 +2244,13 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>4.957690310557267</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="6" t="n">
         <v>-2.60631228742161</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H53" s="7" t="n">
         <v>-516.8789529743534</v>
       </c>
     </row>
@@ -2259,9 +2260,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>600641.XSHG</t>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>600641</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2269,7 +2270,7 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>48.03798999999999</v>
       </c>
       <c r="E54" t="inlineStr">
@@ -2277,13 +2278,13 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="3" t="n">
         <v>49.52439048391855</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>2.988598533934814</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>574.2650659487009</v>
       </c>
     </row>
@@ -2293,9 +2294,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>600666.XSHG</t>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>600666</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2303,7 +2304,7 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>6.026019999999999</v>
       </c>
       <c r="E55" t="inlineStr">
@@ -2311,13 +2312,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>6.144676085217475</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="4" t="n">
         <v>1.86577105923499</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>371.0247327062509</v>
       </c>
     </row>
@@ -2327,9 +2328,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>600673.XSHG</t>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>600673</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2337,7 +2338,7 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>36.48645</v>
       </c>
       <c r="E56" t="inlineStr">
@@ -2345,13 +2346,13 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>36.4860944413856</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="6" t="n">
         <v>-0.1077888675919381</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H56" s="7" t="n">
         <v>-19.66416563974936</v>
       </c>
     </row>
@@ -2361,9 +2362,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>600703.XSHG</t>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>600703</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2371,7 +2372,7 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>13.65364</v>
       </c>
       <c r="E57" t="inlineStr">
@@ -2379,13 +2380,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>14.57433963680438</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>6.63550035043226</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>1268.382262065463</v>
       </c>
     </row>
@@ -2395,9 +2396,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>600703.XSHG</t>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>600703</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2405,7 +2406,7 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>19.3193</v>
       </c>
       <c r="E58" t="inlineStr">
@@ -2413,13 +2414,13 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="3" t="n">
         <v>21.89007856383682</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="4" t="n">
         <v>13.19624122390184</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="5" t="n">
         <v>2549.421430769269</v>
       </c>
     </row>
@@ -2429,9 +2430,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>600844.XSHG</t>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>600844</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2439,7 +2440,7 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>4.174169999999999</v>
       </c>
       <c r="E59" t="inlineStr">
@@ -2447,13 +2448,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="3" t="n">
         <v>4.042859143185698</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="6" t="n">
         <v>-3.247163298375352</v>
       </c>
-      <c r="H59" s="6" t="n">
+      <c r="H59" s="7" t="n">
         <v>-637.0479463834338</v>
       </c>
     </row>
@@ -2463,9 +2464,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>600956.XSHG</t>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>600956</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2473,7 +2474,7 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>9.239229999999999</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -2481,13 +2482,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="3" t="n">
         <v>9.971633878778761</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="4" t="n">
         <v>7.819526610320093</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="5" t="n">
         <v>1517.174501721222</v>
       </c>
     </row>
@@ -2497,9 +2498,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>600975.XSHG</t>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>600975</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2507,7 +2508,7 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>5.92592</v>
       </c>
       <c r="E61" t="inlineStr">
@@ -2515,13 +2516,13 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="3" t="n">
         <v>5.87532865886395</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="6" t="n">
         <v>-0.9564307480083012</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="7" t="n">
         <v>-187.0351592418326</v>
       </c>
     </row>
@@ -2531,9 +2532,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>601138.XSHG</t>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>601138</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2541,7 +2542,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>68.33826999999999</v>
       </c>
       <c r="E62" t="inlineStr">
@@ -2549,13 +2550,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="3" t="n">
         <v>69.22956317127435</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="4" t="n">
         <v>1.178406640023234</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="5" t="n">
         <v>161.0605422714012</v>
       </c>
     </row>
@@ -2565,9 +2566,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>601168.XSHG</t>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>601168</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2575,7 +2576,7 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>35.22518999999999</v>
       </c>
       <c r="E63" t="inlineStr">
@@ -2583,13 +2584,13 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="3" t="n">
         <v>38.30280270281945</v>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="G63" s="4" t="n">
         <v>8.623732111994354</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="5" t="n">
         <v>1518.863010770511</v>
       </c>
     </row>
@@ -2599,9 +2600,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>601226.XSHG</t>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>601226</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2609,7 +2610,7 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>11.27126</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -2617,13 +2618,13 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="3" t="n">
         <v>10.56366396561831</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="G64" s="6" t="n">
         <v>-6.378865970133998</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="7" t="n">
         <v>-1222.263566527053</v>
       </c>
     </row>
@@ -2633,9 +2634,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>601799.XSHG</t>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>601799</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2643,7 +2644,7 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>148.148</v>
       </c>
       <c r="E65" t="inlineStr">
@@ -2651,13 +2652,13 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>147.5510689751348</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G65" s="6" t="n">
         <v>-0.5222234185021359</v>
       </c>
-      <c r="H65" s="6" t="n">
+      <c r="H65" s="7" t="n">
         <v>-77.36635500425443</v>
       </c>
     </row>
@@ -2667,9 +2668,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>603005.XSHG</t>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>603005</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2677,7 +2678,7 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>43.31327</v>
       </c>
       <c r="E66" t="inlineStr">
@@ -2685,13 +2686,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>45.53225945299071</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="4" t="n">
         <v>5.010785073419053</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="5" t="n">
         <v>868.1339471878771</v>
       </c>
     </row>
@@ -2701,9 +2702,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>603063.XSHG</t>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>603063</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2711,7 +2712,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>50.52047</v>
       </c>
       <c r="E67" t="inlineStr">
@@ -2719,13 +2720,13 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="3" t="n">
         <v>55.03845282216061</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G67" s="4" t="n">
         <v>8.820334951729407</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="5" t="n">
         <v>1336.822401956391</v>
       </c>
     </row>
@@ -2735,9 +2736,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>603078.XSHG</t>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>603078</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2745,7 +2746,7 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>31.39136</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -2753,13 +2754,13 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="3" t="n">
         <v>34.66818749708862</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="4" t="n">
         <v>10.32821177928715</v>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="5" t="n">
         <v>1945.29968471906</v>
       </c>
     </row>
@@ -2769,9 +2770,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>603110.XSHG</t>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>603110</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2779,7 +2780,7 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>19.93992</v>
       </c>
       <c r="E69" t="inlineStr">
@@ -2787,13 +2788,13 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="3" t="n">
         <v>22.0429137436142</v>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="G69" s="4" t="n">
         <v>10.43912141274868</v>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="5" t="n">
         <v>2081.552458404956</v>
       </c>
     </row>
@@ -2803,9 +2804,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>603158.XSHG</t>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>603158</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2813,7 +2814,7 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="3" t="n">
         <v>12.45244</v>
       </c>
       <c r="E70" t="inlineStr">
@@ -2821,13 +2822,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" s="3" t="n">
         <v>12.25168872083539</v>
       </c>
-      <c r="G70" s="5" t="n">
+      <c r="G70" s="6" t="n">
         <v>-1.713512892350708</v>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H70" s="7" t="n">
         <v>-341.3986636995784</v>
       </c>
     </row>
@@ -2837,9 +2838,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>603318.XSHG</t>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>603318</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2847,7 +2848,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>9.659649999999999</v>
       </c>
       <c r="E71" t="inlineStr">
@@ -2855,13 +2856,13 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F71" s="3" t="n">
         <v>9.976655484527114</v>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="4" t="n">
         <v>3.176313776689697</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="5" t="n">
         <v>613.6415874600127</v>
       </c>
     </row>
@@ -2871,9 +2872,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>603439.XSHG</t>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>603439</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2881,7 +2882,7 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>16.02601</v>
       </c>
       <c r="E72" t="inlineStr">
@@ -2889,13 +2890,13 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F72" s="3" t="n">
         <v>15.8067342801368</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="6" t="n">
         <v>-1.471549985176591</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" s="7" t="n">
         <v>-282.9968973352788</v>
       </c>
     </row>
@@ -2905,9 +2906,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>603687.XSHG</t>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>603687</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2915,7 +2916,7 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>20.28026</v>
       </c>
       <c r="E73" t="inlineStr">
@@ -2923,13 +2924,13 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="3" t="n">
         <v>21.17252401008425</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="4" t="n">
         <v>4.290635865260113</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>783.1368982152004</v>
       </c>
     </row>
@@ -2939,9 +2940,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>603778.XSHG</t>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>603778</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2949,7 +2950,7 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>21.6216</v>
       </c>
       <c r="E74" t="inlineStr">
@@ -2957,13 +2958,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="3" t="n">
         <v>21.76088997505041</v>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="4" t="n">
         <v>0.5404992879898612</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="5" t="n">
         <v>105.1781346468143</v>
       </c>
     </row>
@@ -2973,9 +2974,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>603778.XSHG</t>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>603778</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2983,7 +2984,7 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>25.025</v>
       </c>
       <c r="E75" t="inlineStr">
@@ -2991,13 +2992,13 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="3" t="n">
         <v>24.88027237973352</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="G75" s="6" t="n">
         <v>-0.6871229708925359</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" s="7" t="n">
         <v>-120.3667664261</v>
       </c>
     </row>
@@ -3007,9 +3008,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>603800.XSHG</t>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>603800</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3017,7 +3018,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>88.11802999999999</v>
       </c>
       <c r="E76" t="inlineStr">
@@ -3025,13 +3026,13 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="3" t="n">
         <v>81.00259149235495</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G76" s="6" t="n">
         <v>-8.179519003779534</v>
       </c>
-      <c r="H76" s="6" t="n">
+      <c r="H76" s="7" t="n">
         <v>-1441.52620192123</v>
       </c>
     </row>
@@ -3041,9 +3042,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>603803.XSHG</t>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>603803</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3051,7 +3052,7 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>15.62561</v>
       </c>
       <c r="E77" t="inlineStr">
@@ -3059,13 +3060,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="3" t="n">
         <v>14.55253115590126</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G77" s="6" t="n">
         <v>-6.969265356178603</v>
       </c>
-      <c r="H77" s="6" t="n">
+      <c r="H77" s="7" t="n">
         <v>-1306.788269305895</v>
       </c>
     </row>
@@ -3075,9 +3076,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>603806.XSHG</t>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>603806</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3085,7 +3086,7 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>19.02901</v>
       </c>
       <c r="E78" t="inlineStr">
@@ -3093,13 +3094,13 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="3" t="n">
         <v>18.3193376566138</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G78" s="6" t="n">
         <v>-3.832072691596038</v>
       </c>
-      <c r="H78" s="6" t="n">
+      <c r="H78" s="7" t="n">
         <v>-729.2054956910792</v>
       </c>
     </row>
@@ -3109,9 +3110,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>603936.XSHG</t>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>603936</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3119,7 +3120,7 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>15.30529</v>
       </c>
       <c r="E79" t="inlineStr">
@@ -3127,13 +3128,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="3" t="n">
         <v>15.38191511403497</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="4" t="n">
         <v>0.3981301676381789</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>79.21546975486224</v>
       </c>
     </row>
@@ -3143,9 +3144,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>605060.XSHG</t>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>605060</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3153,7 +3154,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="3" t="n">
         <v>56.52646999999999</v>
       </c>
       <c r="E80" t="inlineStr">
@@ -3161,13 +3162,13 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="3" t="n">
         <v>52.9961163962626</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="6" t="n">
         <v>-6.353271699316824</v>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H80" s="7" t="n">
         <v>-1077.384066339844</v>
       </c>
     </row>
@@ -3177,9 +3178,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>688137.XSHG</t>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>688137</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3187,7 +3188,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>119.12901</v>
       </c>
       <c r="E81" t="inlineStr">
@@ -3195,13 +3196,13 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="3" t="n">
         <v>125.969037621996</v>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="4" t="n">
         <v>5.602826820023767</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="5" t="n">
         <v>667.4592122708796</v>
       </c>
     </row>
@@ -3211,9 +3212,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>688146.XSHG</t>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>688146</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3221,7 +3222,7 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>52.83277999999999</v>
       </c>
       <c r="E82" t="inlineStr">
@@ -3229,13 +3230,13 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="3" t="n">
         <v>57.80720906942707</v>
       </c>
-      <c r="G82" s="3" t="n">
+      <c r="G82" s="4" t="n">
         <v>9.295527760735547</v>
       </c>
-      <c r="H82" s="4" t="n">
+      <c r="H82" s="5" t="n">
         <v>1473.325719500501</v>
       </c>
     </row>
@@ -3245,9 +3246,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>688158.XSHG</t>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>688158</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3255,7 +3256,7 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>43.04299999999999</v>
       </c>
       <c r="E83" t="inlineStr">
@@ -3263,13 +3264,13 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="3" t="n">
         <v>41.16650649476412</v>
       </c>
-      <c r="G83" s="5" t="n">
+      <c r="G83" s="6" t="n">
         <v>-4.467436873703499</v>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H83" s="7" t="n">
         <v>-769.1675414192787</v>
       </c>
     </row>
@@ -3279,9 +3280,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>688485.XSHG</t>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>688485</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3289,7 +3290,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="3" t="n">
         <v>82.08199999999999</v>
       </c>
       <c r="E84" t="inlineStr">
@@ -3297,13 +3298,13 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="3" t="n">
         <v>86.86603467108546</v>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="G84" s="4" t="n">
         <v>5.712473104216772</v>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="5" t="n">
         <v>937.7824346806422</v>
       </c>
     </row>
@@ -3313,9 +3314,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>688545.XSHG</t>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>688545</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3323,7 +3324,7 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>75.55547999999999</v>
       </c>
       <c r="E85" t="inlineStr">
@@ -3331,13 +3332,13 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="3" t="n">
         <v>90.24069916110533</v>
       </c>
-      <c r="G85" s="3" t="n">
+      <c r="G85" s="4" t="n">
         <v>19.30824984466138</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="5" t="n">
         <v>2917.688169946632</v>
       </c>
     </row>
@@ -3347,9 +3348,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>688584.XSHG</t>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>688584</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3357,7 +3358,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="3" t="n">
         <v>24.44442</v>
       </c>
       <c r="E86" t="inlineStr">
@@ -3365,13 +3366,13 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="3" t="n">
         <v>26.9210411048182</v>
       </c>
-      <c r="G86" s="3" t="n">
+      <c r="G86" s="4" t="n">
         <v>10.023338371926</v>
       </c>
-      <c r="H86" s="4" t="n">
+      <c r="H86" s="5" t="n">
         <v>1960.117543723802</v>
       </c>
     </row>
@@ -3381,9 +3382,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>688593.XSHG</t>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>688593</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3391,7 +3392,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="3" t="n">
         <v>36.2362</v>
       </c>
       <c r="E87" t="inlineStr">
@@ -3399,13 +3400,13 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="3" t="n">
         <v>33.15838725564526</v>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="G87" s="6" t="n">
         <v>-8.596613010898256</v>
       </c>
-      <c r="H87" s="6" t="n">
+      <c r="H87" s="7" t="n">
         <v>-1557.542941927557</v>
       </c>
     </row>
@@ -3415,9 +3416,9 @@
           <t>策略二：单板反包开板2次</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>688596.XSHG</t>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>688596</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3425,7 +3426,7 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>49.43939</v>
       </c>
       <c r="E88" t="inlineStr">
@@ -3433,13 +3434,13 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="3" t="n">
         <v>48.62092605801258</v>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="G88" s="6" t="n">
         <v>-1.75721223133416</v>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H88" s="7" t="n">
         <v>-347.502003270799</v>
       </c>
     </row>
